--- a/data/trans_orig/P25D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>507740</t>
+          <t>507393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>514121</t>
+          <t>514127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1260810</t>
+          <t>1261714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1267707</t>
+          <t>1267708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>29222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,42 +1128,42 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>40243</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>26041</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>60076</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>40243</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>26406</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>59508</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2242213</t>
+          <t>2240389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2270841</t>
+          <t>2270048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2204075</t>
+          <t>2204513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2224593</t>
+          <t>2224635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,42 +1236,42 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4476480</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4456647</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4490682</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>98,67%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4476479</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4457214</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4490316</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4516722</t>
+          <t>4516723</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4516722</t>
+          <t>4516723</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4516722</t>
+          <t>4516723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28039</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622373</t>
+          <t>624401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639293</t>
+          <t>639605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646653</t>
+          <t>646898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655975</t>
+          <t>656045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1276382</t>
+          <t>1274916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293258</t>
+          <t>1293326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55899</t>
+          <t>56074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>35587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83926</t>
+          <t>80124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3386636</t>
+          <t>3386461</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3418841</t>
+          <t>3419113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3611101</t>
+          <t>3611560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3631304</t>
+          <t>3631854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7005756</t>
+          <t>7009558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7045138</t>
+          <t>7045818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>512288</t>
+          <t>575628</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>507393</t>
+          <t>570078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>514127</t>
+          <t>577636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>819957</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1265888</t>
+          <t>1395585</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1261714</t>
+          <t>1389742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1267708</t>
+          <t>1397585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>819957</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>819957</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753600</t>
+          <t>819957</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268538</t>
+          <t>1398486</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268538</t>
+          <t>1398486</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268538</t>
+          <t>1398486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>28257</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>45534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29222</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40243</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60076</t>
+          <t>66371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2259190</t>
+          <t>2194720</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2240389</t>
+          <t>2177443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2270048</t>
+          <t>2205577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2217289</t>
+          <t>2149310</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2204513</t>
+          <t>2138113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2224635</t>
+          <t>2156643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4476480</t>
+          <t>4344030</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4456647</t>
+          <t>4323606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4490682</t>
+          <t>4358922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2282987</t>
+          <t>2222977</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2282987</t>
+          <t>2222977</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2282987</t>
+          <t>2222977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2233735</t>
+          <t>2167000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2233735</t>
+          <t>2167000</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2233735</t>
+          <t>2167000</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4516723</t>
+          <t>4389977</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4516723</t>
+          <t>4389977</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4516723</t>
+          <t>4389977</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>633646</t>
+          <t>698106</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624401</t>
+          <t>688695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639605</t>
+          <t>703997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>652518</t>
+          <t>725914</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646898</t>
+          <t>720081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656045</t>
+          <t>730081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1286162</t>
+          <t>1424021</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274916</t>
+          <t>1413641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293326</t>
+          <t>1431379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644610</t>
+          <t>709555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644610</t>
+          <t>709555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644610</t>
+          <t>709555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659812</t>
+          <t>734168</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659812</t>
+          <t>734168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659812</t>
+          <t>734168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304421</t>
+          <t>1443724</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304421</t>
+          <t>1443724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304421</t>
+          <t>1443724</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43864</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80124</t>
+          <t>89534</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3405124</t>
+          <t>3468455</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3386461</t>
+          <t>3447521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3419113</t>
+          <t>3482188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3623407</t>
+          <t>3695181</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3611560</t>
+          <t>3682029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3631854</t>
+          <t>3703731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7028531</t>
+          <t>7163637</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7009558</t>
+          <t>7142653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7045818</t>
+          <t>7180841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3442535</t>
+          <t>3511061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3442535</t>
+          <t>3511061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3442535</t>
+          <t>3511061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647147</t>
+          <t>3721125</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647147</t>
+          <t>3721125</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647147</t>
+          <t>3721125</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7089682</t>
+          <t>7232187</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7089682</t>
+          <t>7232187</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7089682</t>
+          <t>7232187</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
